--- a/114_teacher_record.xlsx
+++ b/114_teacher_record.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="5" spans="1:9" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>21</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="6" spans="1:9" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>22</v>
@@ -999,8 +999,8 @@
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
-        <v>8</v>
+      <c r="C2" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="24.6" x14ac:dyDescent="0.55000000000000004">
@@ -1010,8 +1010,8 @@
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2">
-        <v>8</v>
+      <c r="C3" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="24.6" x14ac:dyDescent="0.55000000000000004">
@@ -1021,8 +1021,8 @@
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
-        <v>18</v>
+      <c r="C4" s="9">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="24.6" x14ac:dyDescent="0.55000000000000004">
@@ -1032,8 +1032,8 @@
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2">
-        <v>11</v>
+      <c r="C5" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="24.6" x14ac:dyDescent="0.55000000000000004">
@@ -1043,8 +1043,8 @@
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2">
-        <v>7</v>
+      <c r="C6" s="9">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
